--- a/Focus_Analysis_Complete.xlsx
+++ b/Focus_Analysis_Complete.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="241">
   <si>
     <t>x-1_Score%</t>
   </si>
@@ -244,124 +244,118 @@
     <t>56.18</t>
   </si>
   <si>
-    <t>42.63</t>
-  </si>
-  <si>
-    <t>31.42</t>
-  </si>
-  <si>
-    <t>30.17</t>
-  </si>
-  <si>
-    <t>34.41</t>
-  </si>
-  <si>
-    <t>31.72</t>
-  </si>
-  <si>
-    <t>34.83</t>
-  </si>
-  <si>
-    <t>35.58</t>
-  </si>
-  <si>
-    <t>33.10</t>
-  </si>
-  <si>
-    <t>25.67</t>
-  </si>
-  <si>
-    <t>26.10</t>
-  </si>
-  <si>
-    <t>27.46</t>
-  </si>
-  <si>
-    <t>29.78</t>
-  </si>
-  <si>
-    <t>33.96</t>
-  </si>
-  <si>
-    <t>32.08</t>
-  </si>
-  <si>
-    <t>30.75</t>
-  </si>
-  <si>
-    <t>27.71</t>
-  </si>
-  <si>
-    <t>32.60</t>
-  </si>
-  <si>
-    <t>27.77</t>
-  </si>
-  <si>
-    <t>30.91</t>
-  </si>
-  <si>
-    <t>32.54</t>
-  </si>
-  <si>
-    <t>37.89</t>
-  </si>
-  <si>
-    <t>33.25</t>
-  </si>
-  <si>
-    <t>90.84</t>
-  </si>
-  <si>
-    <t>62.15</t>
-  </si>
-  <si>
-    <t>31.95</t>
-  </si>
-  <si>
-    <t>32.10</t>
-  </si>
-  <si>
-    <t>36.18</t>
-  </si>
-  <si>
-    <t>23.78</t>
-  </si>
-  <si>
-    <t>23.57</t>
-  </si>
-  <si>
-    <t>26.23</t>
-  </si>
-  <si>
-    <t>26.82</t>
-  </si>
-  <si>
-    <t>30.53</t>
-  </si>
-  <si>
-    <t>56.97</t>
-  </si>
-  <si>
-    <t>24.45</t>
-  </si>
-  <si>
-    <t>31.78</t>
-  </si>
-  <si>
-    <t>30.51</t>
-  </si>
-  <si>
-    <t>26.52</t>
-  </si>
-  <si>
-    <t>23.26</t>
-  </si>
-  <si>
-    <t>24.19</t>
-  </si>
-  <si>
-    <t>35.56</t>
+    <t>342.19</t>
+  </si>
+  <si>
+    <t>93.81</t>
+  </si>
+  <si>
+    <t>106.72</t>
+  </si>
+  <si>
+    <t>78.25</t>
+  </si>
+  <si>
+    <t>72.87</t>
+  </si>
+  <si>
+    <t>72.31</t>
+  </si>
+  <si>
+    <t>83.75</t>
+  </si>
+  <si>
+    <t>73.93</t>
+  </si>
+  <si>
+    <t>84.26</t>
+  </si>
+  <si>
+    <t>61.10</t>
+  </si>
+  <si>
+    <t>71.33</t>
+  </si>
+  <si>
+    <t>122.70</t>
+  </si>
+  <si>
+    <t>98.48</t>
+  </si>
+  <si>
+    <t>189.20</t>
+  </si>
+  <si>
+    <t>97.50</t>
+  </si>
+  <si>
+    <t>144.92</t>
+  </si>
+  <si>
+    <t>169.72</t>
+  </si>
+  <si>
+    <t>188.04</t>
+  </si>
+  <si>
+    <t>87.49</t>
+  </si>
+  <si>
+    <t>72.28</t>
+  </si>
+  <si>
+    <t>83.78</t>
+  </si>
+  <si>
+    <t>60.87</t>
+  </si>
+  <si>
+    <t>63.87</t>
+  </si>
+  <si>
+    <t>62.76</t>
+  </si>
+  <si>
+    <t>90.52</t>
+  </si>
+  <si>
+    <t>83.25</t>
+  </si>
+  <si>
+    <t>65.68</t>
+  </si>
+  <si>
+    <t>73.70</t>
+  </si>
+  <si>
+    <t>68.21</t>
+  </si>
+  <si>
+    <t>63.38</t>
+  </si>
+  <si>
+    <t>61.65</t>
+  </si>
+  <si>
+    <t>64.46</t>
+  </si>
+  <si>
+    <t>85.58</t>
+  </si>
+  <si>
+    <t>70.55</t>
+  </si>
+  <si>
+    <t>66.02</t>
+  </si>
+  <si>
+    <t>62.35</t>
+  </si>
+  <si>
+    <t>155.63</t>
+  </si>
+  <si>
+    <t>102.62</t>
   </si>
   <si>
     <t>164.40</t>
@@ -451,118 +445,124 @@
     <t>57.18</t>
   </si>
   <si>
-    <t>27.94</t>
-  </si>
-  <si>
-    <t>33.08</t>
-  </si>
-  <si>
-    <t>31.70</t>
-  </si>
-  <si>
-    <t>29.59</t>
-  </si>
-  <si>
-    <t>34.75</t>
-  </si>
-  <si>
-    <t>34.61</t>
-  </si>
-  <si>
-    <t>38.07</t>
-  </si>
-  <si>
-    <t>31.36</t>
-  </si>
-  <si>
-    <t>36.26</t>
-  </si>
-  <si>
-    <t>27.72</t>
-  </si>
-  <si>
-    <t>29.73</t>
-  </si>
-  <si>
-    <t>33.29</t>
-  </si>
-  <si>
-    <t>28.48</t>
-  </si>
-  <si>
-    <t>28.84</t>
-  </si>
-  <si>
-    <t>32.26</t>
-  </si>
-  <si>
-    <t>34.67</t>
-  </si>
-  <si>
-    <t>33.23</t>
-  </si>
-  <si>
-    <t>41.38</t>
-  </si>
-  <si>
-    <t>28.01</t>
-  </si>
-  <si>
-    <t>52.38</t>
-  </si>
-  <si>
-    <t>36.96</t>
-  </si>
-  <si>
-    <t>68.15</t>
-  </si>
-  <si>
-    <t>26.88</t>
-  </si>
-  <si>
-    <t>35.54</t>
-  </si>
-  <si>
-    <t>34.48</t>
-  </si>
-  <si>
-    <t>23.89</t>
-  </si>
-  <si>
-    <t>30.97</t>
-  </si>
-  <si>
-    <t>23.80</t>
-  </si>
-  <si>
-    <t>25.29</t>
-  </si>
-  <si>
-    <t>24.49</t>
-  </si>
-  <si>
-    <t>57.85</t>
-  </si>
-  <si>
-    <t>25.16</t>
-  </si>
-  <si>
-    <t>34.86</t>
-  </si>
-  <si>
-    <t>24.21</t>
-  </si>
-  <si>
-    <t>26.24</t>
-  </si>
-  <si>
-    <t>24.32</t>
-  </si>
-  <si>
-    <t>35.21</t>
-  </si>
-  <si>
-    <t>34.51</t>
+    <t>3.02</t>
+  </si>
+  <si>
+    <t>164.58</t>
+  </si>
+  <si>
+    <t>63.42</t>
+  </si>
+  <si>
+    <t>81.66</t>
+  </si>
+  <si>
+    <t>84.47</t>
+  </si>
+  <si>
+    <t>86.24</t>
+  </si>
+  <si>
+    <t>100.24</t>
+  </si>
+  <si>
+    <t>89.56</t>
+  </si>
+  <si>
+    <t>59.73</t>
+  </si>
+  <si>
+    <t>61.34</t>
+  </si>
+  <si>
+    <t>64.25</t>
+  </si>
+  <si>
+    <t>36.11</t>
+  </si>
+  <si>
+    <t>121.54</t>
+  </si>
+  <si>
+    <t>197.03</t>
+  </si>
+  <si>
+    <t>90.49</t>
+  </si>
+  <si>
+    <t>163.26</t>
+  </si>
+  <si>
+    <t>194.68</t>
+  </si>
+  <si>
+    <t>170.07</t>
+  </si>
+  <si>
+    <t>71.15</t>
+  </si>
+  <si>
+    <t>72.66</t>
+  </si>
+  <si>
+    <t>88.22</t>
+  </si>
+  <si>
+    <t>59.81</t>
+  </si>
+  <si>
+    <t>62.89</t>
+  </si>
+  <si>
+    <t>63.55</t>
+  </si>
+  <si>
+    <t>89.77</t>
+  </si>
+  <si>
+    <t>63.54</t>
+  </si>
+  <si>
+    <t>70.97</t>
+  </si>
+  <si>
+    <t>63.65</t>
+  </si>
+  <si>
+    <t>62.20</t>
+  </si>
+  <si>
+    <t>59.51</t>
+  </si>
+  <si>
+    <t>59.96</t>
+  </si>
+  <si>
+    <t>62.37</t>
+  </si>
+  <si>
+    <t>92.14</t>
+  </si>
+  <si>
+    <t>67.36</t>
+  </si>
+  <si>
+    <t>89.46</t>
+  </si>
+  <si>
+    <t>69.93</t>
+  </si>
+  <si>
+    <t>61.76</t>
+  </si>
+  <si>
+    <t>74.36</t>
+  </si>
+  <si>
+    <t>45.37</t>
+  </si>
+  <si>
+    <t>73.46</t>
   </si>
   <si>
     <t>37.20</t>
@@ -622,100 +622,121 @@
     <t>58.18</t>
   </si>
   <si>
-    <t>28.24</t>
-  </si>
-  <si>
-    <t>33.99</t>
-  </si>
-  <si>
-    <t>31.80</t>
-  </si>
-  <si>
-    <t>41.02</t>
-  </si>
-  <si>
-    <t>33.71</t>
-  </si>
-  <si>
-    <t>34.26</t>
-  </si>
-  <si>
-    <t>26.30</t>
-  </si>
-  <si>
-    <t>29.06</t>
-  </si>
-  <si>
-    <t>32.29</t>
-  </si>
-  <si>
-    <t>34.33</t>
-  </si>
-  <si>
-    <t>29.26</t>
-  </si>
-  <si>
-    <t>27.25</t>
-  </si>
-  <si>
-    <t>29.68</t>
-  </si>
-  <si>
-    <t>38.15</t>
-  </si>
-  <si>
-    <t>26.58</t>
-  </si>
-  <si>
-    <t>28.22</t>
-  </si>
-  <si>
-    <t>26.98</t>
-  </si>
-  <si>
-    <t>27.86</t>
-  </si>
-  <si>
-    <t>33.40</t>
-  </si>
-  <si>
-    <t>64.89</t>
-  </si>
-  <si>
-    <t>27.76</t>
-  </si>
-  <si>
-    <t>24.17</t>
-  </si>
-  <si>
-    <t>24.88</t>
-  </si>
-  <si>
-    <t>23.11</t>
-  </si>
-  <si>
-    <t>26.75</t>
-  </si>
-  <si>
-    <t>76.48</t>
-  </si>
-  <si>
-    <t>26.01</t>
-  </si>
-  <si>
-    <t>26.22</t>
-  </si>
-  <si>
-    <t>33.47</t>
-  </si>
-  <si>
-    <t>24.25</t>
-  </si>
-  <si>
-    <t>23.31</t>
-  </si>
-  <si>
-    <t>24.48</t>
+    <t>26.19</t>
+  </si>
+  <si>
+    <t>57.23</t>
+  </si>
+  <si>
+    <t>200.69</t>
+  </si>
+  <si>
+    <t>77.61</t>
+  </si>
+  <si>
+    <t>81.19</t>
+  </si>
+  <si>
+    <t>78.41</t>
+  </si>
+  <si>
+    <t>74.76</t>
+  </si>
+  <si>
+    <t>99.83</t>
+  </si>
+  <si>
+    <t>97.62</t>
+  </si>
+  <si>
+    <t>60.26</t>
+  </si>
+  <si>
+    <t>69.28</t>
+  </si>
+  <si>
+    <t>93.73</t>
+  </si>
+  <si>
+    <t>61.85</t>
+  </si>
+  <si>
+    <t>144.50</t>
+  </si>
+  <si>
+    <t>99.04</t>
+  </si>
+  <si>
+    <t>95.93</t>
+  </si>
+  <si>
+    <t>82.88</t>
+  </si>
+  <si>
+    <t>150.49</t>
+  </si>
+  <si>
+    <t>70.23</t>
+  </si>
+  <si>
+    <t>62.02</t>
+  </si>
+  <si>
+    <t>89.73</t>
+  </si>
+  <si>
+    <t>64.14</t>
+  </si>
+  <si>
+    <t>60.66</t>
+  </si>
+  <si>
+    <t>88.29</t>
+  </si>
+  <si>
+    <t>77.51</t>
+  </si>
+  <si>
+    <t>86.62</t>
+  </si>
+  <si>
+    <t>70.65</t>
+  </si>
+  <si>
+    <t>73.72</t>
+  </si>
+  <si>
+    <t>63.14</t>
+  </si>
+  <si>
+    <t>61.59</t>
+  </si>
+  <si>
+    <t>67.61</t>
+  </si>
+  <si>
+    <t>61.80</t>
+  </si>
+  <si>
+    <t>60.27</t>
+  </si>
+  <si>
+    <t>65.58</t>
+  </si>
+  <si>
+    <t>66.95</t>
+  </si>
+  <si>
+    <t>62.78</t>
+  </si>
+  <si>
+    <t>71.10</t>
+  </si>
+  <si>
+    <t>90.56</t>
+  </si>
+  <si>
+    <t>146.01</t>
   </si>
 </sst>
 </file>
@@ -1135,22 +1156,22 @@
         <v>76</v>
       </c>
       <c r="F2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G2" t="s">
         <v>60</v>
       </c>
       <c r="H2" t="s">
-        <v>76</v>
+        <v>143</v>
       </c>
       <c r="I2" t="s">
         <v>183</v>
       </c>
       <c r="J2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="K2" t="s">
-        <v>76</v>
+        <v>202</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1168,13 +1189,13 @@
         <v>77</v>
       </c>
       <c r="F3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G3" t="s">
         <v>59</v>
       </c>
       <c r="H3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I3" t="s">
         <v>184</v>
@@ -1183,7 +1204,7 @@
         <v>61</v>
       </c>
       <c r="K3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1201,13 +1222,13 @@
         <v>78</v>
       </c>
       <c r="F4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G4" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I4" t="s">
         <v>29</v>
@@ -1216,7 +1237,7 @@
         <v>192</v>
       </c>
       <c r="K4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1234,13 +1255,13 @@
         <v>79</v>
       </c>
       <c r="F5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G5" t="s">
         <v>58</v>
       </c>
       <c r="H5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I5" t="s">
         <v>42</v>
@@ -1249,7 +1270,7 @@
         <v>62</v>
       </c>
       <c r="K5" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1269,13 +1290,13 @@
         <v>80</v>
       </c>
       <c r="F6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G6" t="s">
         <v>52</v>
       </c>
       <c r="H6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I6" t="s">
         <v>37</v>
@@ -1284,7 +1305,7 @@
         <v>60</v>
       </c>
       <c r="K6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1302,13 +1323,13 @@
         <v>81</v>
       </c>
       <c r="F7" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="G7" t="s">
         <v>59</v>
       </c>
       <c r="H7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I7" t="s">
         <v>40</v>
@@ -1317,7 +1338,7 @@
         <v>61</v>
       </c>
       <c r="K7" t="s">
-        <v>101</v>
+        <v>207</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1341,16 +1362,16 @@
         <v>54</v>
       </c>
       <c r="H8" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I8" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="J8" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="K8" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1368,22 +1389,22 @@
         <v>83</v>
       </c>
       <c r="F9" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G9" t="s">
         <v>62</v>
       </c>
       <c r="H9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I9" t="s">
         <v>46</v>
       </c>
       <c r="J9" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="K9" t="s">
-        <v>156</v>
+        <v>209</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1403,22 +1424,22 @@
         <v>84</v>
       </c>
       <c r="F10" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G10" t="s">
         <v>60</v>
       </c>
       <c r="H10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I10" t="s">
         <v>33</v>
       </c>
       <c r="J10" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="K10" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1442,16 +1463,16 @@
         <v>61</v>
       </c>
       <c r="H11" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I11" t="s">
         <v>30</v>
       </c>
       <c r="J11" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="K11" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1469,22 +1490,22 @@
         <v>86</v>
       </c>
       <c r="F12" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G12" t="s">
         <v>54</v>
       </c>
       <c r="H12" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I12" t="s">
         <v>185</v>
       </c>
       <c r="J12" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="K12" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1508,16 +1529,16 @@
         <v>62</v>
       </c>
       <c r="H13" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I13" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="J13" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="K13" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1537,22 +1558,22 @@
         <v>88</v>
       </c>
       <c r="F14" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="G14" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H14" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I14" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="J14" t="s">
         <v>193</v>
       </c>
       <c r="K14" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1573,10 +1594,10 @@
         <v>38</v>
       </c>
       <c r="G15" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="H15" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I15" t="s">
         <v>29</v>
@@ -1585,7 +1606,7 @@
         <v>194</v>
       </c>
       <c r="K15" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1609,16 +1630,16 @@
         <v>54</v>
       </c>
       <c r="H16" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I16" t="s">
         <v>186</v>
       </c>
       <c r="J16" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="K16" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1639,10 +1660,10 @@
         <v>44</v>
       </c>
       <c r="G17" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="H17" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I17" t="s">
         <v>38</v>
@@ -1651,7 +1672,7 @@
         <v>195</v>
       </c>
       <c r="K17" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1671,13 +1692,13 @@
         <v>92</v>
       </c>
       <c r="F18" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G18" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="H18" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I18" t="s">
         <v>25</v>
@@ -1686,7 +1707,7 @@
         <v>196</v>
       </c>
       <c r="K18" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1704,13 +1725,13 @@
         <v>93</v>
       </c>
       <c r="F19" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G19" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H19" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I19" t="s">
         <v>46</v>
@@ -1719,7 +1740,7 @@
         <v>197</v>
       </c>
       <c r="K19" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1743,16 +1764,16 @@
         <v>68</v>
       </c>
       <c r="H20" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I20" t="s">
         <v>41</v>
       </c>
       <c r="J20" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="K20" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -1773,10 +1794,10 @@
         <v>25</v>
       </c>
       <c r="G21" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H21" t="s">
-        <v>105</v>
+        <v>162</v>
       </c>
       <c r="I21" t="s">
         <v>38</v>
@@ -1785,7 +1806,7 @@
         <v>198</v>
       </c>
       <c r="K21" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -1805,10 +1826,10 @@
         <v>96</v>
       </c>
       <c r="F22" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G22" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="H22" t="s">
         <v>163</v>
@@ -1820,7 +1841,7 @@
         <v>196</v>
       </c>
       <c r="K22" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -1838,7 +1859,7 @@
         <v>97</v>
       </c>
       <c r="F23" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G23" t="s">
         <v>64</v>
@@ -1850,10 +1871,10 @@
         <v>187</v>
       </c>
       <c r="J23" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="K23" t="s">
-        <v>81</v>
+        <v>223</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -1874,7 +1895,7 @@
         <v>30</v>
       </c>
       <c r="G24" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="H24" t="s">
         <v>165</v>
@@ -1886,7 +1907,7 @@
         <v>199</v>
       </c>
       <c r="K24" t="s">
-        <v>98</v>
+        <v>224</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -1907,7 +1928,7 @@
         <v>33</v>
       </c>
       <c r="G25" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H25" t="s">
         <v>166</v>
@@ -1919,7 +1940,7 @@
         <v>198</v>
       </c>
       <c r="K25" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -1951,10 +1972,10 @@
         <v>188</v>
       </c>
       <c r="J26" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="K26" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -1981,13 +2002,13 @@
         <v>168</v>
       </c>
       <c r="I27" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="J27" t="s">
         <v>64</v>
       </c>
       <c r="K27" t="s">
-        <v>171</v>
+        <v>227</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -2008,7 +2029,7 @@
         <v>41</v>
       </c>
       <c r="G28" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="H28" t="s">
         <v>169</v>
@@ -2020,7 +2041,7 @@
         <v>199</v>
       </c>
       <c r="K28" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -2038,10 +2059,10 @@
         <v>103</v>
       </c>
       <c r="F29" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G29" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H29" t="s">
         <v>170</v>
@@ -2053,7 +2074,7 @@
         <v>198</v>
       </c>
       <c r="K29" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -2073,10 +2094,10 @@
         <v>104</v>
       </c>
       <c r="F30" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G30" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="H30" t="s">
         <v>171</v>
@@ -2088,7 +2109,7 @@
         <v>196</v>
       </c>
       <c r="K30" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -2106,7 +2127,7 @@
         <v>105</v>
       </c>
       <c r="F31" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G31" t="s">
         <v>73</v>
@@ -2121,7 +2142,7 @@
         <v>74</v>
       </c>
       <c r="K31" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -2136,10 +2157,10 @@
         <v>72</v>
       </c>
       <c r="E32" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F32" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G32" t="s">
         <v>75</v>
@@ -2151,10 +2172,10 @@
         <v>29</v>
       </c>
       <c r="J32" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="K32" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -2169,7 +2190,7 @@
         <v>55</v>
       </c>
       <c r="E33" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F33" t="s">
         <v>51</v>
@@ -2187,7 +2208,7 @@
         <v>62</v>
       </c>
       <c r="K33" t="s">
-        <v>106</v>
+        <v>233</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -2204,13 +2225,13 @@
         <v>63</v>
       </c>
       <c r="E34" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F34" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G34" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="H34" t="s">
         <v>175</v>
@@ -2222,7 +2243,7 @@
         <v>196</v>
       </c>
       <c r="K34" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -2237,7 +2258,7 @@
         <v>73</v>
       </c>
       <c r="E35" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F35" t="s">
         <v>44</v>
@@ -2249,13 +2270,13 @@
         <v>176</v>
       </c>
       <c r="I35" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="J35" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="K35" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -2270,10 +2291,10 @@
         <v>72</v>
       </c>
       <c r="E36" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F36" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G36" t="s">
         <v>75</v>
@@ -2282,13 +2303,13 @@
         <v>177</v>
       </c>
       <c r="I36" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="J36" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="K36" t="s">
-        <v>229</v>
+        <v>152</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -2303,7 +2324,7 @@
         <v>58</v>
       </c>
       <c r="E37" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F37" t="s">
         <v>42</v>
@@ -2318,10 +2339,10 @@
         <v>190</v>
       </c>
       <c r="J37" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="K37" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -2338,7 +2359,7 @@
         <v>69</v>
       </c>
       <c r="E38" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F38" t="s">
         <v>42</v>
@@ -2353,10 +2374,10 @@
         <v>191</v>
       </c>
       <c r="J38" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="K38" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -2371,13 +2392,13 @@
         <v>74</v>
       </c>
       <c r="E39" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="F39" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G39" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H39" t="s">
         <v>180</v>
@@ -2389,7 +2410,7 @@
         <v>200</v>
       </c>
       <c r="K39" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -2404,13 +2425,13 @@
         <v>75</v>
       </c>
       <c r="E40" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F40" t="s">
         <v>29</v>
       </c>
       <c r="G40" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="H40" t="s">
         <v>181</v>
@@ -2422,7 +2443,7 @@
         <v>201</v>
       </c>
       <c r="K40" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -2437,13 +2458,13 @@
         <v>62</v>
       </c>
       <c r="E41" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F41" t="s">
         <v>42</v>
       </c>
       <c r="G41" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="H41" t="s">
         <v>182</v>
@@ -2455,7 +2476,7 @@
         <v>195</v>
       </c>
       <c r="K41" t="s">
-        <v>82</v>
+        <v>240</v>
       </c>
     </row>
   </sheetData>
